--- a/Andy Hand Deisgn/Fab_hand/FEA Analysis.xlsx
+++ b/Andy Hand Deisgn/Fab_hand/FEA Analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andyc\Documents\GitHub\cad\Andy Hand Deisgn\Fab_hand\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00736AAD-34C8-43CC-BB3B-C1D456C9A45E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{FC07C789-8B9F-43EE-AF1F-B766BFDC25F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{56394538-C017-4FC2-AA3B-24CCEFB4D366}"/>
+    <workbookView xWindow="3552" yWindow="3552" windowWidth="23040" windowHeight="12120" xr2:uid="{56394538-C017-4FC2-AA3B-24CCEFB4D366}"/>
   </bookViews>
   <sheets>
     <sheet name="Table4" sheetId="3" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <definedName name="ExternalData_1" localSheetId="0" hidden="1">Table4!$A$1:$B$73</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -73,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="60">
   <si>
     <t>Type</t>
   </si>
@@ -217,6 +218,42 @@
   </si>
   <si>
     <t>(N)</t>
+  </si>
+  <si>
+    <t>Psi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Von Mises = </t>
+  </si>
+  <si>
+    <t>(32M)/(piD^3)</t>
+  </si>
+  <si>
+    <t>(16*V)/(3*pi*D^2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shear Stress = </t>
+  </si>
+  <si>
+    <t>Bending Normal Stress =</t>
+  </si>
+  <si>
+    <t>sqrt(BNS^2 + 3*SS^2)</t>
+  </si>
+  <si>
+    <t>FOS =</t>
+  </si>
+  <si>
+    <t>Yield Stress / VM</t>
+  </si>
+  <si>
+    <t>Doube Shear =</t>
+  </si>
+  <si>
+    <t>(2*V)/(pi*D^2)</t>
+  </si>
+  <si>
+    <t>(32*M)/(pi*D^3)</t>
   </si>
 </sst>
 </file>
@@ -284,39 +321,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -335,6 +355,21 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -371,11 +406,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5AFA0168-CDFA-4286-A7D1-49E905AF8CD5}" name="Table4_1" displayName="Table4_1" ref="A1:E73" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:E73" xr:uid="{5AFA0168-CDFA-4286-A7D1-49E905AF8CD5}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{2075A080-0164-4635-BECE-C8CCB6895FCA}" uniqueName="1" name="Merged" queryTableFieldId="1" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{B63DF6C4-5180-43EE-BF9C-DFC032CBF38E}" uniqueName="2" name="Unit" queryTableFieldId="2" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{30DE0221-A446-4BEB-A2C3-BC7995E68A1C}" uniqueName="3" name="#" queryTableFieldId="3" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{C7239242-8422-4E19-BB6B-4E0E62217462}" uniqueName="4" name="Connnector" queryTableFieldId="4" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{F89A267A-B5E8-4FB6-856F-5005BAA09E77}" uniqueName="5" name="Joint" queryTableFieldId="5" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{2075A080-0164-4635-BECE-C8CCB6895FCA}" uniqueName="1" name="Merged" queryTableFieldId="1" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{B63DF6C4-5180-43EE-BF9C-DFC032CBF38E}" uniqueName="2" name="Unit" queryTableFieldId="2" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{30DE0221-A446-4BEB-A2C3-BC7995E68A1C}" uniqueName="3" name="#" queryTableFieldId="3" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{C7239242-8422-4E19-BB6B-4E0E62217462}" uniqueName="4" name="Connnector" queryTableFieldId="4" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{F89A267A-B5E8-4FB6-856F-5005BAA09E77}" uniqueName="5" name="Joint" queryTableFieldId="5" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -385,7 +420,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{02E5079D-A3B3-43FA-853B-80C19330E219}" name="Table4" displayName="Table4" ref="A1:H73" totalsRowShown="0">
   <autoFilter ref="A1:H73" xr:uid="{02E5079D-A3B3-43FA-853B-80C19330E219}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{BE8B226C-1937-4521-82C5-8E1B77165DA7}" name="Type" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{BE8B226C-1937-4521-82C5-8E1B77165DA7}" name="Type" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{326FCE08-B08F-4C12-85EB-6A8868B32E28}" name="Column1"/>
     <tableColumn id="3" xr3:uid="{C2427AD6-BC19-464F-8454-54EE2FF468BC}" name="Resultant"/>
     <tableColumn id="4" xr3:uid="{9372A7EA-0EFD-4431-A66D-9C697E1BD4D4}" name="Column2"/>
@@ -723,9 +758,9 @@
     <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
   </cols>
@@ -748,42 +783,42 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>6</v>
       </c>
       <c r="C2">
         <v>8.4466000000000001</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>6</v>
       </c>
       <c r="C3">
         <v>0.18961</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="7" t="str" cm="1">
+      <c r="G3" t="str" cm="1">
         <f t="array" ref="G3:K3" xml:space="preserve"> _xlfn.XLOOKUP(_xlfn.MAXIFS(C2:C26:C44:C53, A2:A26:A44:A53, "Axial Force"),C2:C26:C44:C53,A2:E26:A44:E53)</f>
         <v>Axial Force</v>
       </c>
@@ -808,22 +843,22 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s">
         <v>12</v>
       </c>
       <c r="C4">
         <v>0.68944000000000005</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="7" t="str" cm="1">
+      <c r="G4" t="str" cm="1">
         <f t="array" ref="G4:K4" xml:space="preserve"> _xlfn.XLOOKUP(_xlfn.MAXIFS(C2:C26:C44:C53, A2:A26:A44:A53, "Shear Force"),C2:C26:C44:C53,A2:E26:A44:E53)</f>
         <v>Shear Force</v>
       </c>
@@ -848,19 +883,19 @@
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="2">
         <v>-3.8407E-11</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" t="s">
         <v>29</v>
       </c>
       <c r="G5" t="str" cm="1">
@@ -881,19 +916,19 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" t="s">
         <v>6</v>
       </c>
       <c r="C6">
         <v>34.825000000000003</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" t="s">
         <v>33</v>
       </c>
       <c r="G6" t="str" cm="1">
@@ -914,1303 +949,1401 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" t="s">
         <v>6</v>
       </c>
       <c r="C7">
         <v>1.2361</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8">
         <v>7.1734</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>46</v>
+      <c r="G8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I8">
+        <f>(32*I5)/(PI()*(0.0787)^3)</f>
+        <v>149899.7667255858</v>
+      </c>
+      <c r="J8" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+      <c r="A9" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="2">
         <v>-7.7394999999999995E-11</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" t="s">
         <v>33</v>
       </c>
-      <c r="G9" t="str" cm="1">
-        <f t="array" ref="G9:K9" xml:space="preserve"> _xlfn.XLOOKUP(_xlfn.MAXIFS(C26:C44, A26:A44, "Axial Force"),C26:C44,A26:E44)</f>
-        <v>Axial Force</v>
-      </c>
-      <c r="H9" t="str">
-        <v>(lbf)</v>
+      <c r="G9" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" t="s">
+        <v>58</v>
       </c>
       <c r="I9">
-        <v>1.8559000000000001</v>
-      </c>
-      <c r="J9" t="str">
-        <v>Pin Connector-5</v>
-      </c>
-      <c r="K9" t="str">
-        <v>Joint 1</v>
-      </c>
-      <c r="M9" t="s">
-        <v>47</v>
-      </c>
-      <c r="N9">
-        <f>I9*4.448</f>
-        <v>8.2550432000000011</v>
+        <f>(2*I4)/(PI()*(0.0787)^2)</f>
+        <v>3579.495191509588</v>
+      </c>
+      <c r="J9" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="A10" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" t="s">
         <v>6</v>
       </c>
       <c r="C10">
         <v>34.825000000000003</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" t="s">
         <v>34</v>
       </c>
-      <c r="G10" t="str" cm="1">
-        <f t="array" ref="G10:K10" xml:space="preserve"> _xlfn.XLOOKUP(_xlfn.MAXIFS(C26:C44, A26:A44, "Shear Force"),C26:C44,A26:E44)</f>
-        <v>Shear Force</v>
-      </c>
-      <c r="H10" t="str">
-        <v>(lbf)</v>
+      <c r="G10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" t="s">
+        <v>54</v>
       </c>
       <c r="I10">
-        <v>20.405000000000001</v>
-      </c>
-      <c r="J10" t="str">
-        <v>Pin Connector-4</v>
-      </c>
-      <c r="K10" t="str">
-        <v>Joint 2</v>
-      </c>
-      <c r="M10" t="s">
-        <v>47</v>
-      </c>
-      <c r="N10">
-        <f>I10*4.448</f>
-        <v>90.761440000000007</v>
+        <f>SQRT(I8^2+3*(I9)^2)</f>
+        <v>150027.92547343698</v>
+      </c>
+      <c r="J10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" t="s">
         <v>6</v>
       </c>
       <c r="C11">
         <v>-1.2361</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" t="s">
         <v>34</v>
       </c>
-      <c r="G11" t="str" cm="1">
-        <f t="array" ref="G11:K11" xml:space="preserve"> _xlfn.XLOOKUP(_xlfn.MAXIFS(C26:C44, A26:A44, "Bending moment"),C26:C44,A26:E44)</f>
-        <v>Bending moment</v>
-      </c>
-      <c r="H11" t="str">
-        <v>(lbf.in)</v>
+      <c r="G11" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" t="s">
+        <v>56</v>
       </c>
       <c r="I11">
-        <v>3.8658999999999999</v>
-      </c>
-      <c r="J11" t="str">
-        <v>Pin Connector-4</v>
-      </c>
-      <c r="K11" t="str">
-        <v>Joint 2</v>
+        <f>1/I10</f>
+        <v>6.6654257655322568E-6</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" t="s">
         <v>12</v>
       </c>
       <c r="C12">
         <v>1.0758000000000001</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" t="s">
         <v>34</v>
       </c>
-      <c r="G12" t="str" cm="1">
-        <f t="array" ref="G12:K12" xml:space="preserve"> _xlfn.XLOOKUP(_xlfn.MAXIFS(C26:C44, A26:A44, "Torque "),C26:C44,A26:E44)</f>
-        <v xml:space="preserve">Torque </v>
-      </c>
-      <c r="H12" t="str">
-        <v>(lbf.in)</v>
-      </c>
-      <c r="I12">
-        <v>3.2433000000000001E-12</v>
-      </c>
-      <c r="J12" t="str">
-        <v>Pin Connector-4</v>
-      </c>
-      <c r="K12" t="str">
-        <v>Joint 3</v>
-      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="2">
         <v>-3.7355999999999999E-11</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" t="s">
         <v>28</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" t="s">
         <v>34</v>
       </c>
+      <c r="G13" s="5" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" t="s">
         <v>6</v>
       </c>
       <c r="C14">
         <v>10.833</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="6" t="s">
-        <v>45</v>
+      <c r="G14" t="str" cm="1">
+        <f t="array" ref="G14:K14" xml:space="preserve"> _xlfn.XLOOKUP(_xlfn.MAXIFS(C26:C44, A26:A44, "Axial Force"),C26:C44,A26:E44)</f>
+        <v>Axial Force</v>
+      </c>
+      <c r="H14" t="str">
+        <v>(lbf)</v>
+      </c>
+      <c r="I14">
+        <v>1.8559000000000001</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Pin Connector-5</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Joint 1</v>
+      </c>
+      <c r="M14" t="s">
+        <v>47</v>
+      </c>
+      <c r="N14">
+        <f>I14*4.448</f>
+        <v>8.2550432000000011</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" t="s">
         <v>6</v>
       </c>
       <c r="C15">
         <v>-1.8895</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" t="s">
         <v>29</v>
       </c>
-      <c r="G15" s="7" t="str" cm="1">
-        <f t="array" ref="G15:K15" xml:space="preserve"> _xlfn.XLOOKUP(_xlfn.MAXIFS(C53:C73, A53:A73, "Axial Force"),C53:C73,A53:E73)</f>
-        <v>Axial Force</v>
+      <c r="G15" t="str" cm="1">
+        <f t="array" ref="G15:K15" xml:space="preserve"> _xlfn.XLOOKUP(_xlfn.MAXIFS(C26:C44, A26:A44, "Shear Force"),C26:C44,A26:E44)</f>
+        <v>Shear Force</v>
       </c>
       <c r="H15" t="str">
         <v>(lbf)</v>
       </c>
       <c r="I15">
-        <v>1.8559000000000001</v>
+        <v>20.405000000000001</v>
       </c>
       <c r="J15" t="str">
-        <v>Pin Connector-8</v>
+        <v>Pin Connector-4</v>
       </c>
       <c r="K15" t="str">
-        <v>Joint 1</v>
+        <v>Joint 2</v>
       </c>
       <c r="M15" t="s">
         <v>47</v>
       </c>
       <c r="N15">
         <f>I15*4.448</f>
-        <v>8.2550432000000011</v>
+        <v>90.761440000000007</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" t="s">
         <v>12</v>
       </c>
       <c r="C16">
         <v>7.4079999999999896E-2</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" t="s">
         <v>29</v>
       </c>
       <c r="G16" t="str" cm="1">
-        <f t="array" ref="G16:K16" xml:space="preserve"> _xlfn.XLOOKUP(_xlfn.MAXIFS(C53:C73, A53:A73, "Shear Force"),C53:C73,A53:E73)</f>
-        <v>Shear Force</v>
+        <f t="array" ref="G16:K16" xml:space="preserve"> _xlfn.XLOOKUP(_xlfn.MAXIFS(C26:C44, A26:A44, "Bending moment"),C26:C44,A26:E44)</f>
+        <v>Bending moment</v>
       </c>
       <c r="H16" t="str">
-        <v>(lbf)</v>
+        <v>(lbf.in)</v>
       </c>
       <c r="I16">
-        <v>117.72</v>
+        <v>3.8658999999999999</v>
       </c>
       <c r="J16" t="str">
-        <v>Pin Connector-8</v>
+        <v>Pin Connector-4</v>
       </c>
       <c r="K16" t="str">
-        <v>Joint 1</v>
-      </c>
-      <c r="M16" t="s">
-        <v>47</v>
-      </c>
-      <c r="N16">
-        <f>I16*4.448</f>
-        <v>523.61856</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+        <v>Joint 2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="2">
         <v>4.9308E-12</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" t="s">
         <v>35</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" t="s">
         <v>29</v>
       </c>
       <c r="G17" t="str" cm="1">
-        <f t="array" ref="G17:K17" xml:space="preserve"> _xlfn.XLOOKUP(_xlfn.MAXIFS(C53:C73, A53:A73, "Bending moment"),C53:C73,A53:E73)</f>
-        <v>Bending moment</v>
+        <f t="array" ref="G17:K17" xml:space="preserve"> _xlfn.XLOOKUP(_xlfn.MAXIFS(C26:C44, A26:A44, "Torque "),C26:C44,A26:E44)</f>
+        <v xml:space="preserve">Torque </v>
       </c>
       <c r="H17" t="str">
         <v>(lbf.in)</v>
       </c>
       <c r="I17">
-        <v>94.768000000000001</v>
+        <v>3.2433000000000001E-12</v>
       </c>
       <c r="J17" t="str">
-        <v>Pin Connector-8</v>
+        <v>Pin Connector-4</v>
       </c>
       <c r="K17" t="str">
-        <v>Joint 2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
+        <v>Joint 3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" t="s">
         <v>6</v>
       </c>
       <c r="C18">
         <v>11.114000000000001</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" t="s">
         <v>33</v>
       </c>
-      <c r="G18" t="str" cm="1">
-        <f t="array" ref="G18:K18" xml:space="preserve"> _xlfn.XLOOKUP(_xlfn.MAXIFS(C53:C73, A53:A73, "Torque "),C53:C73,A53:E73)</f>
-        <v xml:space="preserve">Torque </v>
-      </c>
-      <c r="H18" t="str">
-        <v>(lbf.in)</v>
-      </c>
-      <c r="I18">
-        <v>1.5963E-10</v>
-      </c>
-      <c r="J18" t="str">
-        <v>Pin Connector-8</v>
-      </c>
-      <c r="K18" t="str">
-        <v>Joint 1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" t="s">
         <v>6</v>
       </c>
       <c r="C19">
         <v>-1.08</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" t="s">
         <v>12</v>
       </c>
       <c r="C20">
         <v>1.9839</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" t="s">
         <v>35</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="2">
         <v>3.0917999999999997E-11</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" t="s">
         <v>6</v>
       </c>
       <c r="C22">
         <v>11.114000000000001</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" t="s">
         <v>35</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" t="s">
         <v>6</v>
       </c>
       <c r="C23">
         <v>1.08</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" t="s">
         <v>12</v>
       </c>
       <c r="C24">
         <v>0.34658</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" t="s">
         <v>35</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
+      <c r="G24" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="2">
         <v>5.5545999999999998E-12</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" t="s">
         <v>35</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
+      <c r="G25" t="str" cm="1">
+        <f t="array" ref="G25:K25" xml:space="preserve"> _xlfn.XLOOKUP(_xlfn.MAXIFS(C53:C73, A53:A73, "Axial Force"),C53:C73,A53:E73)</f>
+        <v>Axial Force</v>
+      </c>
+      <c r="H25" t="str">
+        <v>(lbf)</v>
+      </c>
+      <c r="I25">
+        <v>1.8559000000000001</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Pin Connector-8</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Joint 1</v>
+      </c>
+      <c r="M25" t="s">
+        <v>47</v>
+      </c>
+      <c r="N25">
+        <f>I25*4.448</f>
+        <v>8.2550432000000011</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" t="s">
         <v>6</v>
       </c>
       <c r="C26">
         <v>10.771000000000001</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" t="s">
         <v>36</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
+      <c r="G26" t="str" cm="1">
+        <f t="array" ref="G26:K26" xml:space="preserve"> _xlfn.XLOOKUP(_xlfn.MAXIFS(C53:C73, A53:A73, "Shear Force"),C53:C73,A53:E73)</f>
+        <v>Shear Force</v>
+      </c>
+      <c r="H26" t="str">
+        <v>(lbf)</v>
+      </c>
+      <c r="I26">
+        <v>117.72</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Pin Connector-8</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Joint 1</v>
+      </c>
+      <c r="M26" t="s">
+        <v>47</v>
+      </c>
+      <c r="N26">
+        <f>I26*4.448</f>
+        <v>523.61856</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" t="s">
         <v>6</v>
       </c>
       <c r="C27">
         <v>1.5063</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" t="s">
         <v>36</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
+      <c r="G27" t="str" cm="1">
+        <f t="array" ref="G27:K27" xml:space="preserve"> _xlfn.XLOOKUP(_xlfn.MAXIFS(C53:C73, A53:A73, "Bending moment"),C53:C73,A53:E73)</f>
+        <v>Bending moment</v>
+      </c>
+      <c r="H27" t="str">
+        <v>(lbf.in)</v>
+      </c>
+      <c r="I27">
+        <v>94.768000000000001</v>
+      </c>
+      <c r="J27" t="str">
+        <v>Pin Connector-8</v>
+      </c>
+      <c r="K27" t="str">
+        <v>Joint 2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" t="s">
         <v>12</v>
       </c>
       <c r="C28">
         <v>0.26972000000000002</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" t="s">
         <v>36</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
+      <c r="G28" t="str" cm="1">
+        <f t="array" ref="G28:K28" xml:space="preserve"> _xlfn.XLOOKUP(_xlfn.MAXIFS(C53:C73, A53:A73, "Torque "),C53:C73,A53:E73)</f>
+        <v xml:space="preserve">Torque </v>
+      </c>
+      <c r="H28" t="str">
+        <v>(lbf.in)</v>
+      </c>
+      <c r="I28">
+        <v>1.5963E-10</v>
+      </c>
+      <c r="J28" t="str">
+        <v>Pin Connector-8</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Joint 1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="2">
         <v>2.6559E-12</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" t="s">
         <v>36</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" t="s">
         <v>6</v>
       </c>
       <c r="C30">
         <v>20.405000000000001</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" t="s">
         <v>36</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
+      <c r="G30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H30" t="s">
+        <v>50</v>
+      </c>
+      <c r="I30">
+        <f>(32*I27)/(PI()*(5/16)^3)</f>
+        <v>31630.915056556289</v>
+      </c>
+      <c r="J30" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" t="s">
         <v>6</v>
       </c>
       <c r="C31">
         <v>0.69686000000000003</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" t="s">
         <v>36</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
+      <c r="G31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H31" t="s">
+        <v>51</v>
+      </c>
+      <c r="I31">
+        <f>(16*I26)/(3*PI()*(5/16)^2)</f>
+        <v>2046.4402323623028</v>
+      </c>
+      <c r="J31" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" t="s">
         <v>12</v>
       </c>
       <c r="C32">
         <v>3.8658999999999999</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" t="s">
         <v>36</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
+      <c r="G32" t="s">
+        <v>49</v>
+      </c>
+      <c r="H32" t="s">
+        <v>54</v>
+      </c>
+      <c r="I32">
+        <f>SQRT(I30^2+3*(I31)^2)</f>
+        <v>31828.894737156246</v>
+      </c>
+      <c r="J32" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="2">
         <v>-2.4505E-11</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" t="s">
         <v>36</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
+      <c r="G33" t="s">
+        <v>55</v>
+      </c>
+      <c r="H33" t="s">
+        <v>56</v>
+      </c>
+      <c r="I33">
+        <f>1/I32</f>
+        <v>3.1417993249782099E-5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>27</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" t="s">
         <v>6</v>
       </c>
       <c r="C34">
         <v>20.405000000000001</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" t="s">
         <v>36</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>30</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" t="s">
         <v>6</v>
       </c>
       <c r="C35">
         <v>-0.69686000000000003</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" t="s">
         <v>36</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="3" t="s">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>31</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" t="s">
         <v>12</v>
       </c>
       <c r="C36">
         <v>0.26798</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" t="s">
         <v>36</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="3" t="s">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>32</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="2">
         <v>3.2433000000000001E-12</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" t="s">
         <v>36</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>27</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" t="s">
         <v>6</v>
       </c>
       <c r="C38">
         <v>16.41</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" t="s">
         <v>37</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="3" t="s">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>30</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" t="s">
         <v>6</v>
       </c>
       <c r="C39">
         <v>1.8559000000000001</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" t="s">
         <v>37</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E39" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>31</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" t="s">
         <v>12</v>
       </c>
       <c r="C40">
         <v>0.31435999999999997</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D40" t="s">
         <v>37</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="E40" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>32</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" t="s">
         <v>12</v>
       </c>
       <c r="C41" s="2">
         <v>-3.71E-11</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" t="s">
         <v>37</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="E41" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="3" t="s">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>27</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" t="s">
         <v>6</v>
       </c>
       <c r="C42">
         <v>16.41</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" t="s">
         <v>37</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="E42" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>30</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" t="s">
         <v>6</v>
       </c>
       <c r="C43">
         <v>-1.8559000000000001</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" t="s">
         <v>37</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="E43" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="3" t="s">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>31</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" t="s">
         <v>12</v>
       </c>
       <c r="C44">
         <v>1.6479999999999999</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" t="s">
         <v>37</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="E44" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>32</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" t="s">
         <v>12</v>
       </c>
       <c r="C45" s="2">
         <v>1.7562999999999999E-11</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" t="s">
         <v>37</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="E45" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="3" t="s">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>27</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" t="s">
         <v>6</v>
       </c>
       <c r="C46">
         <v>16.41</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" t="s">
         <v>38</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="E46" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="3" t="s">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>30</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" t="s">
         <v>6</v>
       </c>
       <c r="C47">
         <v>-1.8559000000000001</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" t="s">
         <v>38</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="E47" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="3" t="s">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>31</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" t="s">
         <v>12</v>
       </c>
       <c r="C48">
         <v>1.0631999999999999</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D48" t="s">
         <v>38</v>
       </c>
-      <c r="E48" s="3" t="s">
+      <c r="E48" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="3" t="s">
+      <c r="A49" t="s">
         <v>32</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" t="s">
         <v>12</v>
       </c>
       <c r="C49" s="2">
         <v>-1.7758000000000001E-11</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D49" t="s">
         <v>38</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="E49" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="3" t="s">
+      <c r="A50" t="s">
         <v>27</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" t="s">
         <v>6</v>
       </c>
       <c r="C50">
         <v>16.41</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="D50" t="s">
         <v>38</v>
       </c>
-      <c r="E50" s="3" t="s">
+      <c r="E50" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="3" t="s">
+      <c r="A51" t="s">
         <v>30</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" t="s">
         <v>6</v>
       </c>
       <c r="C51">
         <v>1.8559000000000001</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D51" t="s">
         <v>38</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="E51" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="3" t="s">
+      <c r="A52" t="s">
         <v>31</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" t="s">
         <v>12</v>
       </c>
       <c r="C52">
         <v>2.9064999999999999</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D52" t="s">
         <v>38</v>
       </c>
-      <c r="E52" s="3" t="s">
+      <c r="E52" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="3" t="s">
+      <c r="A53" t="s">
         <v>32</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="2">
         <v>4.2482000000000003E-11</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="D53" t="s">
         <v>38</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="E53" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="3" t="s">
+      <c r="A54" t="s">
         <v>27</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" t="s">
         <v>6</v>
       </c>
       <c r="C54">
         <v>15.462999999999999</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D54" t="s">
         <v>39</v>
       </c>
-      <c r="E54" s="3" t="s">
+      <c r="E54" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" s="3" t="s">
+      <c r="A55" t="s">
         <v>30</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" t="s">
         <v>6</v>
       </c>
       <c r="C55">
         <v>-0.81838</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="D55" t="s">
         <v>39</v>
       </c>
-      <c r="E55" s="3" t="s">
+      <c r="E55" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="3" t="s">
+      <c r="A56" t="s">
         <v>31</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" t="s">
         <v>12</v>
       </c>
       <c r="C56">
         <v>0.10168000000000001</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="D56" t="s">
         <v>39</v>
       </c>
-      <c r="E56" s="3" t="s">
+      <c r="E56" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="3" t="s">
+      <c r="A57" t="s">
         <v>32</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="2">
         <v>-1.0612E-10</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D57" t="s">
         <v>39</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="E57" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="3" t="s">
+      <c r="A58" t="s">
         <v>27</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" t="s">
         <v>6</v>
       </c>
       <c r="C58">
         <v>15.462999999999999</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="D58" t="s">
         <v>39</v>
       </c>
-      <c r="E58" s="3" t="s">
+      <c r="E58" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" s="3" t="s">
+      <c r="A59" t="s">
         <v>30</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" t="s">
         <v>6</v>
       </c>
       <c r="C59">
         <v>-0.81838</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="D59" t="s">
         <v>39</v>
       </c>
-      <c r="E59" s="3" t="s">
+      <c r="E59" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" s="3" t="s">
+      <c r="A60" t="s">
         <v>31</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" t="s">
         <v>12</v>
       </c>
       <c r="C60">
         <v>1.2665</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="D60" t="s">
         <v>39</v>
       </c>
-      <c r="E60" s="3" t="s">
+      <c r="E60" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="3" t="s">
+      <c r="A61" t="s">
         <v>32</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="2">
         <v>-5.1179999999999998E-11</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="D61" t="s">
         <v>39</v>
       </c>
-      <c r="E61" s="3" t="s">
+      <c r="E61" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" s="3" t="s">
+      <c r="A62" t="s">
         <v>27</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" t="s">
         <v>6</v>
       </c>
       <c r="C62">
         <v>6.8220000000000001</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="D62" t="s">
         <v>39</v>
       </c>
-      <c r="E62" s="3" t="s">
+      <c r="E62" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" s="3" t="s">
+      <c r="A63" t="s">
         <v>30</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" t="s">
         <v>6</v>
       </c>
       <c r="C63">
         <v>1.6277999999999999</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="D63" t="s">
         <v>39</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="E63" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" s="3" t="s">
+      <c r="A64" t="s">
         <v>31</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" t="s">
         <v>12</v>
       </c>
       <c r="C64">
         <v>0.13863</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="D64" t="s">
         <v>39</v>
       </c>
-      <c r="E64" s="3" t="s">
+      <c r="E64" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" s="3" t="s">
+      <c r="A65" t="s">
         <v>32</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" t="s">
         <v>12</v>
       </c>
       <c r="C65" s="2">
         <v>-1.0635E-10</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="D65" t="s">
         <v>39</v>
       </c>
-      <c r="E65" s="3" t="s">
+      <c r="E65" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" s="3" t="s">
+      <c r="A66" t="s">
         <v>27</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" t="s">
         <v>6</v>
       </c>
       <c r="C66">
         <v>117.72</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="D66" t="s">
         <v>40</v>
       </c>
-      <c r="E66" s="3" t="s">
+      <c r="E66" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="3" t="s">
+      <c r="A67" t="s">
         <v>30</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B67" t="s">
         <v>6</v>
       </c>
       <c r="C67">
         <v>1.8559000000000001</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D67" t="s">
         <v>40</v>
       </c>
-      <c r="E67" s="3" t="s">
+      <c r="E67" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="3" t="s">
+      <c r="A68" t="s">
         <v>31</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" t="s">
         <v>12</v>
       </c>
       <c r="C68">
         <v>34.816000000000003</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="D68" t="s">
         <v>40</v>
       </c>
-      <c r="E68" s="3" t="s">
+      <c r="E68" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" s="3" t="s">
+      <c r="A69" t="s">
         <v>32</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B69" t="s">
         <v>12</v>
       </c>
       <c r="C69" s="2">
         <v>1.5963E-10</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="D69" t="s">
         <v>40</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="E69" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70" s="3" t="s">
+      <c r="A70" t="s">
         <v>27</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" t="s">
         <v>6</v>
       </c>
       <c r="C70">
         <v>117.72</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D70" t="s">
         <v>40</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="E70" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" s="3" t="s">
+      <c r="A71" t="s">
         <v>30</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B71" t="s">
         <v>6</v>
       </c>
       <c r="C71">
         <v>-1.8559000000000001</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D71" t="s">
         <v>40</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="E71" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" s="3" t="s">
+      <c r="A72" t="s">
         <v>31</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B72" t="s">
         <v>12</v>
       </c>
       <c r="C72">
         <v>94.768000000000001</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D72" t="s">
         <v>40</v>
       </c>
-      <c r="E72" s="3" t="s">
+      <c r="E72" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" s="3" t="s">
+      <c r="A73" t="s">
         <v>32</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B73" t="s">
         <v>12</v>
       </c>
       <c r="C73" s="2">
         <v>-1.7546E-12</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="D73" t="s">
         <v>40</v>
       </c>
-      <c r="E73" s="3" t="s">
+      <c r="E73" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2238,19 +2371,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="F1" t="s">
